--- a/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
+++ b/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -403,16 +403,16 @@
         </is>
       </c>
       <c r="C2">
-        <v>604884.6580000001</v>
+        <v>552338.677</v>
       </c>
       <c r="D2">
-        <v>587117.323</v>
+        <v>535031.776</v>
       </c>
       <c r="E2">
-        <v>622704.426</v>
+        <v>569595.899</v>
       </c>
       <c r="F2">
-        <v>198.1725046962005</v>
+        <v>170.707184883099</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -432,16 +432,16 @@
         </is>
       </c>
       <c r="C3">
-        <v>35940.072</v>
+        <v>48649.374</v>
       </c>
       <c r="D3">
-        <v>34538.407</v>
+        <v>46583.251</v>
       </c>
       <c r="E3">
-        <v>37361.195</v>
+        <v>50725.869</v>
       </c>
       <c r="F3">
-        <v>-1.855964440581048</v>
+        <v>-13.81377466350667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="C4">
-        <v>47085.236</v>
+        <v>3858.225</v>
       </c>
       <c r="D4">
-        <v>44414.475</v>
+        <v>3653.642</v>
       </c>
       <c r="E4">
-        <v>49916.631</v>
+        <v>4068.359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -487,16 +487,16 @@
         </is>
       </c>
       <c r="C5">
-        <v>12502.744</v>
+        <v>10354.297</v>
       </c>
       <c r="D5">
-        <v>11875.522</v>
+        <v>9829.147000000001</v>
       </c>
       <c r="E5">
-        <v>13142.02</v>
+        <v>10895.875</v>
       </c>
       <c r="F5">
-        <v>-52.05850860602476</v>
+        <v>-57.86000660611119</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -516,16 +516,16 @@
         </is>
       </c>
       <c r="C6">
-        <v>23252.174</v>
+        <v>13311.256</v>
       </c>
       <c r="D6">
-        <v>22102.18</v>
+        <v>12424.124</v>
       </c>
       <c r="E6">
-        <v>24412.371</v>
+        <v>14209.088</v>
       </c>
       <c r="F6">
-        <v>98.36927548066778</v>
+        <v>66.28691617844012</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="C7">
-        <v>41027.609</v>
+        <v>47754.347</v>
       </c>
       <c r="D7">
-        <v>38919.728</v>
+        <v>45340.174</v>
       </c>
       <c r="E7">
-        <v>43216.125</v>
+        <v>50191.991</v>
       </c>
       <c r="F7">
-        <v>-43.33251939006104</v>
+        <v>-43.52198611935816</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -568,22 +568,14 @@
           <t>main</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
       <c r="C8">
-        <v>764692.493</v>
+        <v>76173.152</v>
       </c>
       <c r="D8">
-        <v>738967.635</v>
+        <v>72490.16399999999</v>
       </c>
       <c r="E8">
-        <v>790752.768</v>
-      </c>
-      <c r="F8">
-        <v>114.41650911955</v>
+        <v>79899.19100000001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -594,25 +586,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sc1</t>
+          <t>main</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>All</t>
         </is>
       </c>
       <c r="C9">
-        <v>202863.996</v>
+        <v>676266.176</v>
       </c>
       <c r="D9">
-        <v>196543.072</v>
+        <v>652862.1139999999</v>
       </c>
       <c r="E9">
-        <v>209209.694</v>
+        <v>699687.081</v>
       </c>
       <c r="F9">
-        <v>-66.46236711131795</v>
+        <v>77.57501254759006</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -628,17 +620,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="C10">
-        <v>4318.133</v>
+        <v>204035.47</v>
       </c>
       <c r="D10">
-        <v>3970.713</v>
+        <v>197654.153</v>
       </c>
       <c r="E10">
-        <v>4686.567</v>
+        <v>210461.723</v>
+      </c>
+      <c r="F10">
+        <v>-63.05971707282777</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -654,17 +649,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="C11">
-        <v>2635.507000000001</v>
+        <v>2005.253</v>
       </c>
       <c r="D11">
-        <v>2524.905</v>
+        <v>1860.475</v>
       </c>
       <c r="E11">
-        <v>2750.237</v>
+        <v>2159.205</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -680,20 +675,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C12">
-        <v>36619.72099999999</v>
+        <v>1216.502</v>
       </c>
       <c r="D12">
-        <v>35349.97199999999</v>
+        <v>1160.821</v>
       </c>
       <c r="E12">
-        <v>37897.425</v>
-      </c>
-      <c r="F12">
-        <v>1.891061876559375</v>
+        <v>1274.188</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -709,20 +701,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="C13">
-        <v>26079.172</v>
+        <v>56446.80900000001</v>
       </c>
       <c r="D13">
-        <v>25300.53999999999</v>
+        <v>54481.049</v>
       </c>
       <c r="E13">
-        <v>26868.49799999999</v>
+        <v>58423.515</v>
       </c>
       <c r="F13">
-        <v>108.587586852934</v>
+        <v>16.02782185850943</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -738,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="C14">
-        <v>11721.661</v>
+        <v>24571.188</v>
       </c>
       <c r="D14">
-        <v>11178.246</v>
+        <v>23784.819</v>
       </c>
       <c r="E14">
-        <v>12280.096</v>
+        <v>25367.948</v>
       </c>
       <c r="F14">
-        <v>-49.58896746600984</v>
+        <v>137.3042612163819</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -767,20 +759,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="C15">
-        <v>72400.62299999999</v>
+        <v>8004.993</v>
       </c>
       <c r="D15">
-        <v>69674.46400000001</v>
+        <v>7537.941000000001</v>
       </c>
       <c r="E15">
-        <v>75196.823</v>
+        <v>8483.770999999999</v>
       </c>
       <c r="F15">
-        <v>76.46805350026612</v>
+        <v>-39.86297761834044</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -796,20 +788,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="C16">
-        <v>356638.813</v>
+        <v>84553.87100000001</v>
       </c>
       <c r="D16">
-        <v>344541.9119999999</v>
+        <v>81461.851</v>
       </c>
       <c r="E16">
-        <v>368889.34</v>
+        <v>87694.54599999997</v>
       </c>
       <c r="F16">
-        <v>-53.36180016612246</v>
+        <v>77.06005067978421</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -820,7 +812,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sc2</t>
+          <t>sc1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -829,16 +821,16 @@
         </is>
       </c>
       <c r="C17">
-        <v>741009.755</v>
+        <v>380834.086</v>
       </c>
       <c r="D17">
-        <v>717338.655</v>
+        <v>367941.1089999999</v>
       </c>
       <c r="E17">
-        <v>764807.0440000001</v>
+        <v>393864.896</v>
       </c>
       <c r="F17">
-        <v>-3.097027657102946</v>
+        <v>-43.68577055671049</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -849,27 +841,56 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>sc2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>729658.1990000001</v>
+      </c>
+      <c r="D18">
+        <v>705760.902</v>
+      </c>
+      <c r="E18">
+        <v>753705.5319999999</v>
+      </c>
+      <c r="F18">
+        <v>7.895119539440068</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>sc3</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="C18">
-        <v>650563.9820000001</v>
-      </c>
-      <c r="D18">
-        <v>628286.041</v>
-      </c>
-      <c r="E18">
-        <v>673019.3289999999</v>
-      </c>
-      <c r="F18">
-        <v>-14.9247589122076</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="C19">
+        <v>594505.8160000001</v>
+      </c>
+      <c r="D19">
+        <v>573079.789</v>
+      </c>
+      <c r="E19">
+        <v>615998.8119999999</v>
+      </c>
+      <c r="F19">
+        <v>-12.08996736811511</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>tot_daly</t>
         </is>

--- a/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
+++ b/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
@@ -1,21 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Sensitivity analyses/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2896A797-DF61-8C46-BA4C-AB8AB6393003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="17700" windowHeight="12860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="20">
+  <si>
+    <t>analysis</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>relative_perc_daly</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>sc1</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>sc2</t>
+  </si>
+  <si>
+    <t>sc3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +147,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +199,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +233,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +268,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,173 +444,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>relative_perc_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>552338.677</v>
+        <v>552338.67700000003</v>
       </c>
       <c r="D2">
-        <v>535031.776</v>
+        <v>535031.77599999995</v>
       </c>
       <c r="E2">
-        <v>569595.899</v>
+        <v>569595.89899999998</v>
       </c>
       <c r="F2">
-        <v>170.707184883099</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+        <v>170.70718488309899</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>48649.374</v>
+        <v>48649.374000000003</v>
       </c>
       <c r="D3">
-        <v>46583.251</v>
+        <v>46583.250999999997</v>
       </c>
       <c r="E3">
-        <v>50725.869</v>
+        <v>50725.868999999999</v>
       </c>
       <c r="F3">
         <v>-13.81377466350667</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>3858.225</v>
+        <v>3858.2249999999999</v>
       </c>
       <c r="D4">
-        <v>3653.642</v>
+        <v>3653.6419999999998</v>
       </c>
       <c r="E4">
-        <v>4068.359</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+        <v>4068.3589999999999</v>
+      </c>
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
         <v>10354.297</v>
       </c>
       <c r="D5">
-        <v>9829.147000000001</v>
+        <v>9829.1470000000008</v>
       </c>
       <c r="E5">
         <v>10895.875</v>
       </c>
       <c r="F5">
-        <v>-57.86000660611119</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+        <v>-57.860006606111192</v>
+      </c>
+      <c r="G5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>13311.256</v>
+        <v>13311.255999999999</v>
       </c>
       <c r="D6">
         <v>12424.124</v>
@@ -525,375 +577,280 @@
         <v>14209.088</v>
       </c>
       <c r="F6">
-        <v>66.28691617844012</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>66.286916178440123</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>47754.347</v>
+        <v>47754.347000000002</v>
       </c>
       <c r="D7">
-        <v>45340.174</v>
+        <v>45340.173999999999</v>
       </c>
       <c r="E7">
-        <v>50191.991</v>
+        <v>50191.991000000002</v>
       </c>
       <c r="F7">
-        <v>-43.52198611935816</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
+        <v>-43.521986119358161</v>
+      </c>
+      <c r="G7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>76173.152</v>
+        <v>676266.17599999998</v>
       </c>
       <c r="D8">
-        <v>72490.16399999999</v>
+        <v>652862.11399999994</v>
       </c>
       <c r="E8">
-        <v>79899.19100000001</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>699687.08100000001</v>
+      </c>
+      <c r="F8">
+        <v>77.575012547590063</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>676266.176</v>
+        <v>204035.47</v>
       </c>
       <c r="D9">
-        <v>652862.1139999999</v>
+        <v>197654.15299999999</v>
       </c>
       <c r="E9">
-        <v>699687.081</v>
+        <v>210461.723</v>
       </c>
       <c r="F9">
-        <v>77.57501254759006</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+        <v>-63.059717072827773</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>204035.47</v>
+        <v>2005.2529999999999</v>
       </c>
       <c r="D10">
-        <v>197654.153</v>
+        <v>1860.4749999999999</v>
       </c>
       <c r="E10">
-        <v>210461.723</v>
-      </c>
-      <c r="F10">
-        <v>-63.05971707282777</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+        <v>2159.2049999999999</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>2005.253</v>
+        <v>1216.502</v>
       </c>
       <c r="D11">
-        <v>1860.475</v>
+        <v>1160.8209999999999</v>
       </c>
       <c r="E11">
-        <v>2159.205</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
+        <v>1274.1880000000001</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>1216.502</v>
+        <v>56446.809000000008</v>
       </c>
       <c r="D12">
-        <v>1160.821</v>
+        <v>54481.048999999999</v>
       </c>
       <c r="E12">
-        <v>1274.188</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+        <v>58423.514999999999</v>
+      </c>
+      <c r="F12">
+        <v>16.02782185850943</v>
+      </c>
+      <c r="G12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>56446.80900000001</v>
+        <v>24571.187999999998</v>
       </c>
       <c r="D13">
-        <v>54481.049</v>
+        <v>23784.819</v>
       </c>
       <c r="E13">
-        <v>58423.515</v>
+        <v>25367.948</v>
       </c>
       <c r="F13">
-        <v>16.02782185850943</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+        <v>137.30426121638189</v>
+      </c>
+      <c r="G13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>24571.188</v>
+        <v>8004.9930000000004</v>
       </c>
       <c r="D14">
-        <v>23784.819</v>
+        <v>7537.9410000000007</v>
       </c>
       <c r="E14">
-        <v>25367.948</v>
+        <v>8483.7709999999988</v>
       </c>
       <c r="F14">
-        <v>137.3042612163819</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+        <v>-39.862977618340437</v>
+      </c>
+      <c r="G14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>8004.993</v>
+        <v>84553.871000000014</v>
       </c>
       <c r="D15">
-        <v>7537.941000000001</v>
+        <v>81461.850999999995</v>
       </c>
       <c r="E15">
-        <v>8483.770999999999</v>
+        <v>87694.545999999973</v>
       </c>
       <c r="F15">
-        <v>-39.86297761834044</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>77.060050679784212</v>
+      </c>
+      <c r="G15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>84553.87100000001</v>
+        <v>380834.08600000001</v>
       </c>
       <c r="D16">
-        <v>81461.851</v>
+        <v>367941.10899999988</v>
       </c>
       <c r="E16">
-        <v>87694.54599999997</v>
+        <v>393864.89600000001</v>
       </c>
       <c r="F16">
-        <v>77.06005067978421</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sc1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>-43.685770556710487</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
       </c>
       <c r="C17">
-        <v>380834.086</v>
+        <v>729658.19900000014</v>
       </c>
       <c r="D17">
-        <v>367941.1089999999</v>
+        <v>705760.902</v>
       </c>
       <c r="E17">
-        <v>393864.896</v>
+        <v>753705.53199999989</v>
       </c>
       <c r="F17">
-        <v>-43.68577055671049</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>sc2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>7.8951195394400679</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>729658.1990000001</v>
+        <v>594505.81600000011</v>
       </c>
       <c r="D18">
-        <v>705760.902</v>
+        <v>573079.78899999999</v>
       </c>
       <c r="E18">
-        <v>753705.5319999999</v>
+        <v>615998.81199999992</v>
       </c>
       <c r="F18">
-        <v>7.895119539440068</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sc3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>594505.8160000001</v>
-      </c>
-      <c r="D19">
-        <v>573079.789</v>
-      </c>
-      <c r="E19">
-        <v>615998.8119999999</v>
-      </c>
-      <c r="F19">
         <v>-12.08996736811511</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
+      <c r="G18" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
